--- a/data/trans_dic/P1408-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1408-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -717,52 +717,52 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 11,0</t>
+          <t>7,41; 11,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,76</t>
+          <t>3,75; 6,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,28</t>
+          <t>3,22; 6,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,74</t>
+          <t>6,74; 10,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,95</t>
+          <t>3,64; 5,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,23</t>
+          <t>1,65; 3,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,67</t>
+          <t>1,53; 3,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,85</t>
+          <t>4,32; 6,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,64</t>
+          <t>5,63; 7,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 4,32</t>
+          <t>2,82; 4,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 8,36</t>
+          <t>5,63; 7,84</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,91</t>
+          <t>1,52; 2,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,88</t>
+          <t>0,71; 1,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,79</t>
+          <t>1,08; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,29</t>
+          <t>1,03; 2,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,04</t>
+          <t>0,24; 1,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,38</t>
+          <t>0,52; 1,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,54</t>
+          <t>1,46; 2,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,38</t>
+          <t>1,44; 2,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,37</t>
+          <t>0,59; 1,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,48</t>
+          <t>0,82; 1,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,05</t>
+          <t>1,42; 2,23</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,64</t>
+          <t>0,54; 2,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,8</t>
+          <t>0,16; 2,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,84</t>
+          <t>0,49; 1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,63</t>
+          <t>0,41; 2,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,93</t>
+          <t>0,53; 1,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,18</t>
+          <t>0,66; 2,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,37</t>
+          <t>0,26; 1,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,57</t>
+          <t>0,61; 1,5</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,82</t>
+          <t>3,54; 4,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,74</t>
+          <t>1,67; 2,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,54</t>
+          <t>1,51; 2,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,9</t>
+          <t>2,06; 3,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,33</t>
+          <t>2,2; 3,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,64</t>
+          <t>0,84; 1,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,7</t>
+          <t>0,91; 1,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,97</t>
+          <t>2,17; 3,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 3,9</t>
+          <t>3,0; 3,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,01</t>
+          <t>1,35; 2,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,96</t>
+          <t>1,33; 1,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,8</t>
+          <t>2,25; 2,91</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47882</t>
+          <t>50446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41649</t>
+          <t>44398</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89531</t>
+          <t>94845</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77866; 113460</t>
+          <t>76427; 113793</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>37726; 65911</t>
+          <t>36517; 64967</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24869; 47358</t>
+          <t>24298; 47564</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36877; 60341</t>
+          <t>38923; 62944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>47563; 78301</t>
+          <t>47814; 78263</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21253; 43156</t>
+          <t>22079; 44976</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16115; 36507</t>
+          <t>15261; 35844</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33022; 51409</t>
+          <t>35316; 54140</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132156; 179186</t>
+          <t>132168; 177933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66485; 99740</t>
+          <t>65132; 100696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45335; 75273</t>
+          <t>45233; 75218</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75135; 105750</t>
+          <t>78532; 109388</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29289</t>
+          <t>32836</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39999</t>
+          <t>43793</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69288</t>
+          <t>76629</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25430; 49264</t>
+          <t>25817; 50243</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14096; 36853</t>
+          <t>13902; 36638</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19102; 40311</t>
+          <t>19179; 40377</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18946; 40993</t>
+          <t>24018; 44380</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16117; 36389</t>
+          <t>16323; 35524</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5089; 18229</t>
+          <t>4165; 18493</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9683; 27441</t>
+          <t>10376; 27852</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26975; 56884</t>
+          <t>31728; 59228</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47136; 78243</t>
+          <t>47186; 77062</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22820; 51024</t>
+          <t>21843; 49514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33380; 60230</t>
+          <t>33449; 61148</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54082; 92848</t>
+          <t>62483; 97948</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>7629</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>14341</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3429; 14573</t>
+          <t>2958; 13315</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1930,52 +1930,52 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>895; 9844</t>
+          <t>891; 11440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3413; 11909</t>
+          <t>3466; 12021</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1924; 12516</t>
+          <t>1944; 13174</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4866</t>
+          <t>0; 5165</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>984; 8247</t>
+          <t>985; 8213</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3491; 12711</t>
+          <t>3875; 13036</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6926; 22423</t>
+          <t>6788; 21788</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4839</t>
+          <t>0; 5099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2794; 15000</t>
+          <t>2820; 15567</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8463; 20509</t>
+          <t>8781; 21742</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>83692</t>
+          <t>89995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>95820</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>172262</t>
+          <t>185815</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>113437; 157978</t>
+          <t>116127; 161980</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57801; 93576</t>
+          <t>57101; 93365</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>51343; 85632</t>
+          <t>51151; 84308</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>62832; 100192</t>
+          <t>72619; 106812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>73793; 112672</t>
+          <t>74356; 110814</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30954; 58197</t>
+          <t>29922; 57088</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31823; 60044</t>
+          <t>32251; 59873</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>69103; 108220</t>
+          <t>80722; 114532</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>198466; 259841</t>
+          <t>199435; 257911</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>95473; 139918</t>
+          <t>94139; 139935</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91225; 135195</t>
+          <t>91898; 135976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>143673; 198782</t>
+          <t>162624; 210565</t>
         </is>
       </c>
     </row>
